--- a/Data/EXCEL/Transfer/salemon/202206/6827-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6827-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1967528C-4DD2-4E71-AC50-C9D65D867B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{383844AE-3A62-4B11-B959-3D8C5451884C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6827-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -1218,17 +1218,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.25" customWidth="1"/>
-    <col min="2" max="2" width="11.125" customWidth="1"/>
-    <col min="3" max="3" width="10.625" customWidth="1"/>
-    <col min="4" max="5" width="11.125" customWidth="1"/>
-    <col min="6" max="6" width="10.625" customWidth="1"/>
-    <col min="7" max="7" width="12.125" customWidth="1"/>
-    <col min="8" max="16" width="10.625" customWidth="1"/>
-    <col min="17" max="17" width="11.125" customWidth="1"/>
+    <col min="1" max="1" width="15.125" customWidth="1"/>
+    <col min="2" max="5" width="12.75" customWidth="1"/>
+    <col min="6" max="6" width="12.125" customWidth="1"/>
+    <col min="7" max="7" width="13.875" customWidth="1"/>
+    <col min="8" max="16" width="12.125" customWidth="1"/>
+    <col min="17" max="17" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1381,25 +1379,25 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>27</v>
+        <v>24.9</v>
       </c>
       <c r="C5" s="7">
-        <v>24.9</v>
+        <v>19.25</v>
       </c>
       <c r="D5" s="7">
-        <v>27.05</v>
+        <v>27.1</v>
       </c>
       <c r="E5" s="7">
-        <v>22.95</v>
+        <v>19</v>
       </c>
       <c r="F5" s="8">
-        <v>-2.1</v>
+        <v>-5.65</v>
       </c>
       <c r="G5" s="8">
-        <v>-7.78</v>
+        <v>-22.69</v>
       </c>
       <c r="H5" s="9">
         <v>0</v>
@@ -1434,25 +1432,25 @@
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C6" s="7">
-        <v>27</v>
+        <v>24.9</v>
       </c>
       <c r="D6" s="7">
-        <v>31.25</v>
+        <v>27.05</v>
       </c>
       <c r="E6" s="7">
-        <v>26</v>
+        <v>22.95</v>
       </c>
       <c r="F6" s="8">
-        <v>-3</v>
+        <v>-2.1</v>
       </c>
       <c r="G6" s="8">
-        <v>-10</v>
+        <v>-7.78</v>
       </c>
       <c r="H6" s="9">
         <v>0</v>
@@ -1487,25 +1485,25 @@
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="C7" s="7">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D7" s="7">
-        <v>32.9</v>
+        <v>31.25</v>
       </c>
       <c r="E7" s="7">
-        <v>28.4</v>
+        <v>26</v>
       </c>
       <c r="F7" s="8">
-        <v>-2.5</v>
+        <v>-3</v>
       </c>
       <c r="G7" s="8">
-        <v>-7.69</v>
+        <v>-10</v>
       </c>
       <c r="H7" s="9">
         <v>0</v>
@@ -1540,25 +1538,25 @@
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>31.6</v>
+        <v>32.5</v>
       </c>
       <c r="C8" s="7">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="D8" s="7">
-        <v>36.1</v>
+        <v>32.9</v>
       </c>
       <c r="E8" s="7">
-        <v>31</v>
-      </c>
-      <c r="F8" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="G8" s="10">
-        <v>2.85</v>
+        <v>28.4</v>
+      </c>
+      <c r="F8" s="8">
+        <v>-2.5</v>
+      </c>
+      <c r="G8" s="8">
+        <v>-7.69</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -1593,25 +1591,25 @@
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>33.1</v>
+        <v>31.6</v>
       </c>
       <c r="C9" s="7">
-        <v>31.6</v>
+        <v>32.5</v>
       </c>
       <c r="D9" s="7">
-        <v>33.85</v>
+        <v>36.1</v>
       </c>
       <c r="E9" s="7">
-        <v>30.25</v>
-      </c>
-      <c r="F9" s="8">
-        <v>-1.5</v>
-      </c>
-      <c r="G9" s="8">
-        <v>-4.53</v>
+        <v>31</v>
+      </c>
+      <c r="F9" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="G9" s="10">
+        <v>2.85</v>
       </c>
       <c r="H9" s="9">
         <v>0</v>
@@ -1646,25 +1644,25 @@
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>31.5</v>
+        <v>33.1</v>
       </c>
       <c r="C10" s="7">
-        <v>33.1</v>
+        <v>31.6</v>
       </c>
       <c r="D10" s="7">
-        <v>39.1</v>
+        <v>33.85</v>
       </c>
       <c r="E10" s="7">
-        <v>30.4</v>
-      </c>
-      <c r="F10" s="10">
-        <v>1.6</v>
-      </c>
-      <c r="G10" s="10">
-        <v>5.08</v>
+        <v>30.25</v>
+      </c>
+      <c r="F10" s="8">
+        <v>-1.5</v>
+      </c>
+      <c r="G10" s="8">
+        <v>-4.53</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -1699,25 +1697,25 @@
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>32.700000000000003</v>
+        <v>31.5</v>
       </c>
       <c r="C11" s="7">
-        <v>31.5</v>
+        <v>33.1</v>
       </c>
       <c r="D11" s="7">
-        <v>33.200000000000003</v>
+        <v>39.1</v>
       </c>
       <c r="E11" s="7">
-        <v>24.3</v>
-      </c>
-      <c r="F11" s="8">
-        <v>-1.2</v>
-      </c>
-      <c r="G11" s="8">
-        <v>-3.67</v>
+        <v>30.4</v>
+      </c>
+      <c r="F11" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="G11" s="10">
+        <v>5.08</v>
       </c>
       <c r="H11" s="9">
         <v>0</v>
@@ -1752,25 +1750,25 @@
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>38.15</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="C12" s="7">
-        <v>32.700000000000003</v>
+        <v>31.5</v>
       </c>
       <c r="D12" s="7">
-        <v>51.8</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="E12" s="7">
-        <v>31.5</v>
+        <v>24.3</v>
       </c>
       <c r="F12" s="8">
-        <v>-5.45</v>
+        <v>-1.2</v>
       </c>
       <c r="G12" s="8">
-        <v>-14.29</v>
+        <v>-3.67</v>
       </c>
       <c r="H12" s="9">
         <v>0</v>
@@ -1805,25 +1803,25 @@
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>17</v>
+        <v>44470</v>
+      </c>
+      <c r="B13" s="7">
+        <v>38.15</v>
+      </c>
+      <c r="C13" s="7">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="D13" s="7">
+        <v>51.8</v>
+      </c>
+      <c r="E13" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="F13" s="8">
+        <v>-5.45</v>
+      </c>
+      <c r="G13" s="8">
+        <v>-14.29</v>
       </c>
       <c r="H13" s="9">
         <v>0</v>
@@ -1858,7 +1856,7 @@
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>17</v>
@@ -1911,7 +1909,7 @@
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>17</v>
@@ -1964,7 +1962,7 @@
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>17</v>
@@ -2017,7 +2015,7 @@
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>17</v>
@@ -2070,7 +2068,7 @@
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>17</v>
@@ -2123,7 +2121,7 @@
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>17</v>
@@ -2176,7 +2174,7 @@
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>17</v>
@@ -2229,54 +2227,107 @@
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
+        <v>44228</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="9">
+        <v>0</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" s="9">
+        <v>0</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M21" s="9">
+        <v>0</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P21" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
         <v>44197</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21" s="9">
-        <v>0</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K21" s="9">
-        <v>0</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M21" s="9">
-        <v>0</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P21" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="9" t="s">
+      <c r="B22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="9">
+        <v>0</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K22" s="9">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M22" s="9">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P22" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="9" t="s">
         <v>17</v>
       </c>
     </row>
